--- a/artifacts/YUNZ-20/selftest/stage7/browser/蓉城战役WBS-20261014.xlsx
+++ b/artifacts/YUNZ-20/selftest/stage7/browser/蓉城战役WBS-20261014.xlsx
@@ -16743,6 +16743,9 @@
       <c r="H1" t="str">
         <v>被阻塞(填写计划完成时间)</v>
       </c>
+      <c r="M1" t="str">
+        <v>导出日期：2026-10-14 20:35</v>
+      </c>
     </row>
     <row r="2">
       <c r="D2" t="str">
